--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-LOG-MedicationDispense.xlsx
@@ -323,9 +323,6 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>GEM-ERP-LOG-MedicationDispense.prescriptionId</t>
   </si>
   <si>
@@ -379,6 +376,9 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense.medication.medicationArzneimittel</t>
@@ -1936,21 +1936,21 @@
         <v>77</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1976,10 +1976,10 @@
         <v>85</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2030,7 +2030,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>84</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2076,13 +2076,13 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2133,7 +2133,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>84</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2179,13 +2179,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2236,7 +2236,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>84</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2464,14 +2464,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2484,25 +2484,25 @@
         <v>75</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2551,7 +2551,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2560,13 +2560,13 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -2597,7 +2597,7 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>119</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2900,25 +2900,25 @@
         <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -2967,7 +2967,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2976,13 +2976,13 @@
         <v>77</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -3116,7 +3116,7 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>128</v>
@@ -3324,7 +3324,7 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>133</v>
@@ -3947,7 +3947,7 @@
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>144</v>
@@ -4020,7 +4020,7 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>81</v>
@@ -4054,7 +4054,7 @@
         <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>85</v>
@@ -4472,7 +4472,7 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>163</v>
@@ -4579,7 +4579,7 @@
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>85</v>
@@ -4684,10 +4684,10 @@
         <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>177</v>
@@ -4789,7 +4789,7 @@
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>85</v>
@@ -4896,7 +4896,7 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>125</v>
@@ -5314,7 +5314,7 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>163</v>
@@ -5421,7 +5421,7 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>85</v>
@@ -5526,10 +5526,10 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>200</v>
@@ -5631,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>85</v>
@@ -5738,7 +5738,7 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>125</v>
@@ -6156,7 +6156,7 @@
         <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>163</v>
@@ -6263,7 +6263,7 @@
         <v>75</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>85</v>
@@ -6368,10 +6368,10 @@
         <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>211</v>
@@ -6473,7 +6473,7 @@
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>85</v>
@@ -6580,7 +6580,7 @@
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>125</v>
@@ -6998,7 +6998,7 @@
         <v>75</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>163</v>
@@ -7105,7 +7105,7 @@
         <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>85</v>
@@ -7210,10 +7210,10 @@
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>222</v>
@@ -7315,7 +7315,7 @@
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>85</v>
@@ -7422,7 +7422,7 @@
         <v>75</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K57" t="s" s="2">
         <v>125</v>
@@ -7840,7 +7840,7 @@
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>163</v>
@@ -7947,7 +7947,7 @@
         <v>75</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>85</v>
@@ -8052,10 +8052,10 @@
         <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>233</v>
@@ -8157,7 +8157,7 @@
         <v>75</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>85</v>
@@ -8264,7 +8264,7 @@
         <v>75</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>125</v>
@@ -8785,7 +8785,7 @@
         <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>144</v>
@@ -8858,7 +8858,7 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>81</v>
@@ -8892,7 +8892,7 @@
         <v>75</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>85</v>
@@ -9310,7 +9310,7 @@
         <v>75</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>163</v>
@@ -9417,7 +9417,7 @@
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K76" t="s" s="2">
         <v>85</v>
@@ -9522,10 +9522,10 @@
         <v>75</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>251</v>
@@ -9627,7 +9627,7 @@
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>85</v>
@@ -9734,7 +9734,7 @@
         <v>75</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K79" t="s" s="2">
         <v>125</v>
@@ -10152,7 +10152,7 @@
         <v>75</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>163</v>
@@ -10259,7 +10259,7 @@
         <v>75</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>85</v>
@@ -10364,10 +10364,10 @@
         <v>75</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>233</v>
@@ -10469,7 +10469,7 @@
         <v>75</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>85</v>
@@ -10576,7 +10576,7 @@
         <v>75</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>125</v>
@@ -10994,7 +10994,7 @@
         <v>75</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>163</v>
@@ -11101,7 +11101,7 @@
         <v>75</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>85</v>
@@ -11206,10 +11206,10 @@
         <v>75</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>270</v>
@@ -11311,7 +11311,7 @@
         <v>75</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>85</v>
@@ -11418,7 +11418,7 @@
         <v>75</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>125</v>
@@ -11736,7 +11736,7 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L98" t="s" s="2">
         <v>279</v>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12039,25 +12039,25 @@
         <v>75</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
@@ -12106,7 +12106,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -12115,13 +12115,13 @@
         <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102">
@@ -12255,7 +12255,7 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>285</v>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -12560,25 +12560,25 @@
         <v>75</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
@@ -12627,7 +12627,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -12636,13 +12636,13 @@
         <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107">
@@ -12981,7 +12981,7 @@
         <v>75</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K110" t="s" s="2">
         <v>144</v>
@@ -13054,7 +13054,7 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>81</v>
@@ -13088,7 +13088,7 @@
         <v>75</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K111" t="s" s="2">
         <v>85</v>
@@ -13506,7 +13506,7 @@
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>163</v>
@@ -13613,7 +13613,7 @@
         <v>75</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>85</v>
@@ -13718,10 +13718,10 @@
         <v>75</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L117" t="s" s="2">
         <v>177</v>
@@ -13823,7 +13823,7 @@
         <v>75</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>85</v>
@@ -13930,7 +13930,7 @@
         <v>75</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>125</v>
@@ -14348,7 +14348,7 @@
         <v>75</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K123" t="s" s="2">
         <v>163</v>
@@ -14455,7 +14455,7 @@
         <v>75</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>85</v>
@@ -14560,10 +14560,10 @@
         <v>75</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>200</v>
@@ -14665,7 +14665,7 @@
         <v>75</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>85</v>
@@ -14772,7 +14772,7 @@
         <v>75</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K127" t="s" s="2">
         <v>125</v>
@@ -15190,7 +15190,7 @@
         <v>75</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>163</v>
@@ -15297,7 +15297,7 @@
         <v>75</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>85</v>
@@ -15402,10 +15402,10 @@
         <v>75</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L133" t="s" s="2">
         <v>211</v>
@@ -15507,7 +15507,7 @@
         <v>75</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>85</v>
@@ -15614,7 +15614,7 @@
         <v>75</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>125</v>
@@ -16032,7 +16032,7 @@
         <v>75</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K139" t="s" s="2">
         <v>163</v>
@@ -16139,7 +16139,7 @@
         <v>75</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K140" t="s" s="2">
         <v>85</v>
@@ -16244,10 +16244,10 @@
         <v>75</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>222</v>
@@ -16349,7 +16349,7 @@
         <v>75</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>85</v>
@@ -16456,7 +16456,7 @@
         <v>75</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K143" t="s" s="2">
         <v>125</v>
@@ -16874,7 +16874,7 @@
         <v>75</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K147" t="s" s="2">
         <v>163</v>
@@ -16981,7 +16981,7 @@
         <v>75</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>85</v>
@@ -17086,10 +17086,10 @@
         <v>75</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L149" t="s" s="2">
         <v>233</v>
@@ -17191,7 +17191,7 @@
         <v>75</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K150" t="s" s="2">
         <v>85</v>
@@ -17298,7 +17298,7 @@
         <v>75</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K151" t="s" s="2">
         <v>125</v>
@@ -17820,7 +17820,7 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>346</v>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
@@ -18127,25 +18127,25 @@
         <v>75</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K159" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N159" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>75</v>
@@ -18194,7 +18194,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -18203,13 +18203,13 @@
         <v>77</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="160">
@@ -19171,7 +19171,7 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>371</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
@@ -19476,25 +19476,25 @@
         <v>75</v>
       </c>
       <c r="I172" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K172" t="s" s="2">
         <v>91</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N172" t="s" s="2">
         <v>94</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>75</v>
@@ -19543,7 +19543,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -19552,13 +19552,13 @@
         <v>77</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="173">
